--- a/Q2_2026_Spending_.xlsx
+++ b/Q2_2026_Spending_.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbook/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4834E9E6-C0F9-1441-AA2E-135351643B72}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6FCE0D-D51B-B04C-BCED-C248CCB545F8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="KOLs 2026" sheetId="1" r:id="rId1"/>
+    <sheet name="KOLs Spending" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KOLs 2026'!$A$1:$AA$244</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KOLs Spending'!$A$1:$AA$244</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
